--- a/artfynd/A 55825-2024 artfynd.xlsx
+++ b/artfynd/A 55825-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121589409</v>
+        <v>121589408</v>
       </c>
       <c r="B2" t="n">
-        <v>97059</v>
+        <v>78345</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>648535</v>
+        <v>648517</v>
       </c>
       <c r="R2" t="n">
-        <v>7167621</v>
+        <v>7167742</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121589408</v>
+        <v>121589399</v>
       </c>
       <c r="B4" t="n">
-        <v>78345</v>
+        <v>57356</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>648517</v>
+        <v>648299</v>
       </c>
       <c r="R4" t="n">
-        <v>7167742</v>
+        <v>7167446</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,12 +966,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Gamla ringhack på gammalt grantorrträd</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121589399</v>
+        <v>121589409</v>
       </c>
       <c r="B5" t="n">
-        <v>57356</v>
+        <v>97059</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1010,25 +1015,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1042,10 +1047,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>648299</v>
+        <v>648535</v>
       </c>
       <c r="R5" t="n">
-        <v>7167446</v>
+        <v>7167621</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1072,17 +1077,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Gamla ringhack på gammalt grantorrträd</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 55825-2024 artfynd.xlsx
+++ b/artfynd/A 55825-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121589408</v>
+        <v>121589399</v>
       </c>
       <c r="B2" t="n">
-        <v>78345</v>
+        <v>57356</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>648517</v>
+        <v>648299</v>
       </c>
       <c r="R2" t="n">
-        <v>7167742</v>
+        <v>7167446</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,12 +749,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Gamla ringhack på gammalt grantorrträd</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -892,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121589399</v>
+        <v>121589408</v>
       </c>
       <c r="B4" t="n">
-        <v>57356</v>
+        <v>78345</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -936,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>648299</v>
+        <v>648517</v>
       </c>
       <c r="R4" t="n">
-        <v>7167446</v>
+        <v>7167742</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -966,17 +971,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gamla ringhack på gammalt grantorrträd</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 55825-2024 artfynd.xlsx
+++ b/artfynd/A 55825-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121589399</v>
+        <v>121589409</v>
       </c>
       <c r="B2" t="n">
-        <v>57356</v>
+        <v>97067</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>648299</v>
+        <v>648535</v>
       </c>
       <c r="R2" t="n">
-        <v>7167446</v>
+        <v>7167621</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,17 +749,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Gamla ringhack på gammalt grantorrträd</t>
+          <t>2024-08-12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121589400</v>
+        <v>121589399</v>
       </c>
       <c r="B3" t="n">
-        <v>57372</v>
+        <v>57357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,16 +797,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -830,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>648381</v>
+        <v>648299</v>
       </c>
       <c r="R3" t="n">
-        <v>7167468</v>
+        <v>7167446</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -870,7 +865,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Födosökshack i gammal tallhögstubbe</t>
+          <t>Gamla ringhack på gammalt grantorrträd</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,7 +895,7 @@
         <v>121589408</v>
       </c>
       <c r="B4" t="n">
-        <v>78345</v>
+        <v>78352</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1003,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121589409</v>
+        <v>121589400</v>
       </c>
       <c r="B5" t="n">
-        <v>97059</v>
+        <v>57373</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1015,25 +1010,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1047,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>648535</v>
+        <v>648381</v>
       </c>
       <c r="R5" t="n">
-        <v>7167621</v>
+        <v>7167468</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1077,12 +1072,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Födosökshack i gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 55825-2024 artfynd.xlsx
+++ b/artfynd/A 55825-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121589408</v>
+        <v>121589409</v>
       </c>
       <c r="B2" t="n">
-        <v>78352</v>
+        <v>97067</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>648517</v>
+        <v>648535</v>
       </c>
       <c r="R2" t="n">
-        <v>7167742</v>
+        <v>7167621</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121589400</v>
+        <v>121589399</v>
       </c>
       <c r="B3" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,16 +797,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>648381</v>
+        <v>648299</v>
       </c>
       <c r="R3" t="n">
-        <v>7167468</v>
+        <v>7167446</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -865,7 +865,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Födosökshack i gammal tallhögstubbe</t>
+          <t>Gamla ringhack på gammalt grantorrträd</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121589409</v>
+        <v>121589408</v>
       </c>
       <c r="B4" t="n">
-        <v>97067</v>
+        <v>78352</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,25 +904,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>648535</v>
+        <v>648517</v>
       </c>
       <c r="R4" t="n">
-        <v>7167621</v>
+        <v>7167742</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -998,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121589399</v>
+        <v>121589400</v>
       </c>
       <c r="B5" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,16 +1014,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1042,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>648299</v>
+        <v>648381</v>
       </c>
       <c r="R5" t="n">
-        <v>7167446</v>
+        <v>7167468</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Gamla ringhack på gammalt grantorrträd</t>
+          <t>Födosökshack i gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 55825-2024 artfynd.xlsx
+++ b/artfynd/A 55825-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121589409</v>
+        <v>121589408</v>
       </c>
       <c r="B2" t="n">
-        <v>97067</v>
+        <v>78352</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>648535</v>
+        <v>648517</v>
       </c>
       <c r="R2" t="n">
-        <v>7167621</v>
+        <v>7167742</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121589399</v>
+        <v>121589400</v>
       </c>
       <c r="B3" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,16 +797,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>648299</v>
+        <v>648381</v>
       </c>
       <c r="R3" t="n">
-        <v>7167446</v>
+        <v>7167468</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -865,7 +865,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Gamla ringhack på gammalt grantorrträd</t>
+          <t>Födosökshack i gammal tallhögstubbe</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121589408</v>
+        <v>121589409</v>
       </c>
       <c r="B4" t="n">
-        <v>78352</v>
+        <v>97067</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -904,25 +904,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -936,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>648517</v>
+        <v>648535</v>
       </c>
       <c r="R4" t="n">
-        <v>7167742</v>
+        <v>7167621</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -998,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121589400</v>
+        <v>121589399</v>
       </c>
       <c r="B5" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,16 +1014,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1042,10 +1042,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>648381</v>
+        <v>648299</v>
       </c>
       <c r="R5" t="n">
-        <v>7167468</v>
+        <v>7167446</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Födosökshack i gammal tallhögstubbe</t>
+          <t>Gamla ringhack på gammalt grantorrträd</t>
         </is>
       </c>
       <c r="AD5" t="b">
